--- a/booking.xlsx
+++ b/booking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>NIK</t>
   </si>
@@ -381,21 +381,11 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -419,21 +409,11 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>

--- a/booking.xlsx
+++ b/booking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>NIK</t>
   </si>
@@ -28,82 +28,19 @@
     <t>Worksite</t>
   </si>
   <si>
-    <t>027810</t>
+    <t>021543</t>
   </si>
   <si>
-    <t>CAESARIUS FEBRIANTO</t>
+    <t>nama</t>
   </si>
   <si>
-    <t>Product Management Division Head (Funding, Wealth, Treasury &amp; Corporate)</t>
+    <t>divisi</t>
   </si>
   <si>
-    <t>caesarius.febrianto@banksinarmas.com</t>
+    <t>e@mail.com</t>
   </si>
   <si>
     <t>GOP 1</t>
-  </si>
-  <si>
-    <t>019343</t>
-  </si>
-  <si>
-    <t>SENDY TANUSA PUTRA</t>
-  </si>
-  <si>
-    <t>sendy.t.putra@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>019561</t>
-  </si>
-  <si>
-    <t>SANTRI MAY CHATRIN SIHOMBING</t>
-  </si>
-  <si>
-    <t>santri.c.sihombing@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>028329</t>
-  </si>
-  <si>
-    <t>OLIVIA DWI LESTARI</t>
-  </si>
-  <si>
-    <t>olivia.d.lestari@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>019088</t>
-  </si>
-  <si>
-    <t>RANI ANGGREYNI</t>
-  </si>
-  <si>
-    <t>rani.anggreyni@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>021502</t>
-  </si>
-  <si>
-    <t>TRENGGONO</t>
-  </si>
-  <si>
-    <t>trenggono@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>017787</t>
-  </si>
-  <si>
-    <t>VERAWATI</t>
-  </si>
-  <si>
-    <t>verawati@banksinarmas.com</t>
-  </si>
-  <si>
-    <t>022565</t>
-  </si>
-  <si>
-    <t>AYUB MANAHAN ZINA</t>
-  </si>
-  <si>
-    <t>ayub.m.zina@banksinarmas.com</t>
   </si>
 </sst>
 </file>
@@ -444,21 +381,11 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -482,21 +409,11 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -520,21 +437,11 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -558,21 +465,11 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -596,21 +493,11 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -634,21 +521,11 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -672,21 +549,11 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -28401,34 +28268,6 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
-    <row r="999">
-      <c r="A999" s="1"/>
-      <c r="B999" s="1"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-      <c r="H999" s="1"/>
-      <c r="I999" s="1"/>
-      <c r="J999" s="1"/>
-      <c r="K999" s="1"/>
-      <c r="L999" s="1"/>
-      <c r="M999" s="1"/>
-      <c r="N999" s="1"/>
-      <c r="O999" s="1"/>
-      <c r="P999" s="1"/>
-      <c r="Q999" s="1"/>
-      <c r="R999" s="1"/>
-      <c r="S999" s="1"/>
-      <c r="T999" s="1"/>
-      <c r="U999" s="1"/>
-      <c r="V999" s="1"/>
-      <c r="W999" s="1"/>
-      <c r="X999" s="1"/>
-      <c r="Y999" s="1"/>
-      <c r="Z999" s="1"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/booking.xlsx
+++ b/booking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>NIK</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>GOP 1</t>
+  </si>
+  <si>
+    <t>021544</t>
   </si>
 </sst>
 </file>
@@ -381,11 +384,21 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>

--- a/booking.xlsx
+++ b/booking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>NIK</t>
   </si>
@@ -28,22 +28,82 @@
     <t>Worksite</t>
   </si>
   <si>
-    <t>021543</t>
+    <t>027810</t>
   </si>
   <si>
-    <t>nama</t>
+    <t>CAESARIUS FEBRIANTO</t>
   </si>
   <si>
-    <t>divisi</t>
+    <t>Product Management Division Head (Funding, Wealth, Treasury &amp; Corporate)</t>
   </si>
   <si>
-    <t>e@mail.com</t>
+    <t>caesarius.febrianto@banksinarmas.com</t>
   </si>
   <si>
     <t>GOP 1</t>
   </si>
   <si>
-    <t>021544</t>
+    <t>019343</t>
+  </si>
+  <si>
+    <t>SENDY TANUSA PUTRA</t>
+  </si>
+  <si>
+    <t>sendy.t.putra@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>019561</t>
+  </si>
+  <si>
+    <t>SANTRI MAY CHATRIN SIHOMBING</t>
+  </si>
+  <si>
+    <t>santri.c.sihombing@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>028329</t>
+  </si>
+  <si>
+    <t>OLIVIA DWI LESTARI</t>
+  </si>
+  <si>
+    <t>olivia.d.lestari@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>019088</t>
+  </si>
+  <si>
+    <t>RANI ANGGREYNI</t>
+  </si>
+  <si>
+    <t>rani.anggreyni@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>021502</t>
+  </si>
+  <si>
+    <t>TRENGGONO</t>
+  </si>
+  <si>
+    <t>trenggono@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>017787</t>
+  </si>
+  <si>
+    <t>VERAWATI</t>
+  </si>
+  <si>
+    <t>verawati@banksinarmas.com</t>
+  </si>
+  <si>
+    <t>022565</t>
+  </si>
+  <si>
+    <t>AYUB MANAHAN ZINA</t>
+  </si>
+  <si>
+    <t>ayub.m.zina@banksinarmas.com</t>
   </si>
 </sst>
 </file>
@@ -388,13 +448,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -422,11 +482,21 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -450,11 +520,21 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -478,11 +558,21 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -506,11 +596,21 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -534,11 +634,21 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -562,11 +672,21 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -28281,6 +28401,34 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
+    <row r="999">
+      <c r="A999" s="1"/>
+      <c r="B999" s="1"/>
+      <c r="C999" s="1"/>
+      <c r="D999" s="1"/>
+      <c r="E999" s="1"/>
+      <c r="F999" s="1"/>
+      <c r="G999" s="1"/>
+      <c r="H999" s="1"/>
+      <c r="I999" s="1"/>
+      <c r="J999" s="1"/>
+      <c r="K999" s="1"/>
+      <c r="L999" s="1"/>
+      <c r="M999" s="1"/>
+      <c r="N999" s="1"/>
+      <c r="O999" s="1"/>
+      <c r="P999" s="1"/>
+      <c r="Q999" s="1"/>
+      <c r="R999" s="1"/>
+      <c r="S999" s="1"/>
+      <c r="T999" s="1"/>
+      <c r="U999" s="1"/>
+      <c r="V999" s="1"/>
+      <c r="W999" s="1"/>
+      <c r="X999" s="1"/>
+      <c r="Y999" s="1"/>
+      <c r="Z999" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
